--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,10 +501,10 @@
         <v>1147500</v>
       </c>
       <c r="E2" t="n">
-        <v>7.95</v>
+        <v>7.8</v>
       </c>
       <c r="F2" t="n">
-        <v>596250</v>
+        <v>585000</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -513,7 +513,7 @@
         <v>6.21</v>
       </c>
       <c r="I2" t="n">
-        <v>11.95</v>
+        <v>12.18</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -538,25 +538,25 @@
         <v>534750</v>
       </c>
       <c r="E3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="F3" t="n">
-        <v>565800</v>
+        <v>527850</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>9.91</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>52978.2</v>
+        <v>52357.2</v>
       </c>
     </row>
     <row r="4">
@@ -599,186 +599,186 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3BBIF</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120000</v>
+        <v>105000</v>
       </c>
       <c r="C5" t="n">
-        <v>10.1</v>
+        <v>4.48</v>
       </c>
       <c r="D5" t="n">
-        <v>1212000</v>
+        <v>470400</v>
       </c>
       <c r="E5" t="n">
-        <v>6.55</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>786000</v>
+        <v>178500</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>5.11</v>
+        <v>3.09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.88</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>61908</v>
+        <v>14521.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105000</v>
+        <v>120000</v>
       </c>
       <c r="C6" t="n">
-        <v>4.48</v>
+        <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>470400</v>
+        <v>1212000</v>
       </c>
       <c r="E6" t="n">
-        <v>1.81</v>
+        <v>6.4</v>
       </c>
       <c r="F6" t="n">
-        <v>190050</v>
+        <v>768000</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.09</v>
+        <v>4.96</v>
       </c>
       <c r="I6" t="n">
-        <v>7.64</v>
+        <v>7.83</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>14521.5</v>
+        <v>60156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>PROSPECT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="C7" t="n">
-        <v>8.699999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>435000</v>
+        <v>291000</v>
       </c>
       <c r="E7" t="n">
-        <v>8.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="F7" t="n">
-        <v>410000</v>
+        <v>303000</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>6.59</v>
+        <v>7.43</v>
       </c>
       <c r="I7" t="n">
-        <v>6.99</v>
+        <v>7.14</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>28650</v>
+        <v>21630</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PROSPECT</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="C8" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>188000</v>
+        <v>435000</v>
       </c>
       <c r="E8" t="n">
-        <v>10.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>208000</v>
+        <v>422500</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>7.68</v>
+        <v>6.71</v>
       </c>
       <c r="I8" t="n">
-        <v>6.94</v>
+        <v>6.91</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>14430</v>
+        <v>29195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27000</v>
+        <v>55000</v>
       </c>
       <c r="C9" t="n">
-        <v>7.45</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>201150</v>
+        <v>990000</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="F9" t="n">
-        <v>121500</v>
+        <v>726000</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.16</v>
+        <v>5.05</v>
       </c>
       <c r="I9" t="n">
-        <v>6.89</v>
+        <v>6.88</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>8370</v>
+        <v>49967.5</v>
       </c>
     </row>
     <row r="10">
@@ -797,10 +797,10 @@
         <v>182500</v>
       </c>
       <c r="E10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>172500</v>
+        <v>175000</v>
       </c>
       <c r="G10" t="n">
         <v>11</v>
@@ -809,13 +809,13 @@
         <v>6.37</v>
       </c>
       <c r="I10" t="n">
-        <v>6.74</v>
+        <v>6.65</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>11620</v>
+        <v>11632.5</v>
       </c>
     </row>
     <row r="11">
@@ -834,10 +834,10 @@
         <v>113000</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F11" t="n">
-        <v>123000</v>
+        <v>124000</v>
       </c>
       <c r="G11" t="n">
         <v>12</v>
@@ -846,7 +846,7 @@
         <v>7.26</v>
       </c>
       <c r="I11" t="n">
-        <v>6.67</v>
+        <v>6.61</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -858,38 +858,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>WHART</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>12.3</v>
       </c>
       <c r="D12" t="n">
-        <v>990000</v>
+        <v>246000</v>
       </c>
       <c r="E12" t="n">
-        <v>13.4</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>737000</v>
+        <v>220000</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.75</v>
+        <v>5.68</v>
       </c>
       <c r="I12" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>47003</v>
+        <v>13974</v>
       </c>
     </row>
     <row r="13">
@@ -908,10 +908,10 @@
         <v>240000</v>
       </c>
       <c r="E13" t="n">
-        <v>38.5</v>
+        <v>40.75</v>
       </c>
       <c r="F13" t="n">
-        <v>288750</v>
+        <v>305625</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -920,50 +920,13 @@
         <v>7.19</v>
       </c>
       <c r="I13" t="n">
-        <v>5.97</v>
+        <v>5.64</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
       </c>
       <c r="K13" t="n">
         <v>17250</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WHART</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C14" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>246000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>228000</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>13548</v>
       </c>
     </row>
   </sheetData>

--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,38 +488,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>PROSPECT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75000</v>
+        <v>37500</v>
       </c>
       <c r="C2" t="n">
-        <v>15.3</v>
+        <v>9.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1147500</v>
+        <v>360000</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>585000</v>
+        <v>337500</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>6.21</v>
+        <v>10.44</v>
       </c>
       <c r="I2" t="n">
-        <v>12.18</v>
+        <v>11.14</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>71250</v>
+        <v>37593.75</v>
       </c>
     </row>
     <row r="3">
@@ -529,34 +529,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69000</v>
+        <v>72000</v>
       </c>
       <c r="C3" t="n">
         <v>7.75</v>
       </c>
       <c r="D3" t="n">
-        <v>534750</v>
+        <v>558000</v>
       </c>
       <c r="E3" t="n">
-        <v>7.65</v>
+        <v>7.05</v>
       </c>
       <c r="F3" t="n">
-        <v>527850</v>
+        <v>507600</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>9.92</v>
+        <v>10.76</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>52357.2</v>
+        <v>54633.6</v>
       </c>
     </row>
     <row r="4">
@@ -566,367 +566,182 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="C4" t="n">
-        <v>12.7</v>
+        <v>12.35</v>
       </c>
       <c r="D4" t="n">
-        <v>571500</v>
+        <v>617500</v>
       </c>
       <c r="E4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="F4" t="n">
-        <v>459000</v>
+        <v>455000</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
-        <v>8.710000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>39996</v>
+        <v>44440</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105000</v>
+        <v>50000</v>
       </c>
       <c r="C5" t="n">
-        <v>4.48</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>470400</v>
+        <v>435000</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>7.9</v>
       </c>
       <c r="F5" t="n">
-        <v>178500</v>
+        <v>395000</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.09</v>
+        <v>6.71</v>
       </c>
       <c r="I5" t="n">
-        <v>8.140000000000001</v>
+        <v>7.39</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>14521.5</v>
+        <v>29195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3BBIF</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120000</v>
+        <v>7500</v>
       </c>
       <c r="C6" t="n">
-        <v>10.1</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>1212000</v>
+        <v>240000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.4</v>
+        <v>40.75</v>
       </c>
       <c r="F6" t="n">
-        <v>768000</v>
+        <v>305625</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.96</v>
+        <v>8.75</v>
       </c>
       <c r="I6" t="n">
-        <v>7.83</v>
+        <v>6.87</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>60156</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PROSPECT</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="C7" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="D7" t="n">
-        <v>291000</v>
+        <v>252000</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>6.85</v>
       </c>
       <c r="F7" t="n">
-        <v>303000</v>
+        <v>239750</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>7.43</v>
+        <v>6.46</v>
       </c>
       <c r="I7" t="n">
-        <v>7.14</v>
+        <v>6.79</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>21630</v>
+        <v>16285.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>WHART</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="C8" t="n">
-        <v>8.699999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="D8" t="n">
-        <v>435000</v>
+        <v>246000</v>
       </c>
       <c r="E8" t="n">
-        <v>8.449999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="F8" t="n">
-        <v>422500</v>
+        <v>208000</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>6.71</v>
+        <v>5.68</v>
       </c>
       <c r="I8" t="n">
-        <v>6.91</v>
+        <v>6.72</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>29195</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CPNREIT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>55000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D9" t="n">
-        <v>990000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>726000</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>49967.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TFFIF</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>25000</v>
-      </c>
-      <c r="C10" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>182500</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>175000</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>11632.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AIMIRT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C11" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>113000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F11" t="n">
-        <v>124000</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8200</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WHART</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>246000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>220000</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
         <v>13974</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C13" t="n">
-        <v>32</v>
-      </c>
-      <c r="D13" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E13" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="F13" t="n">
-        <v>305625</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17250</v>
       </c>
     </row>
   </sheetData>
